--- a/github pro 1.xlsx
+++ b/github pro 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/73AA32B96C5CB0FC/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/73aa32b96c5cb0fc/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{01E96CC6-881E-4FD9-BE80-B4E4673F1A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="14_{01E96CC6-881E-4FD9-BE80-B4E4673F1A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E9966B2-8C37-4113-A819-B998A94EE267}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{57112942-4356-491A-B7B3-BEB1B5171BDD}"/>
   </bookViews>
@@ -3283,7 +3283,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D2:D50 G2:G50">
-    <cfRule type="colorScale" priority="19">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3295,7 +3295,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G50">
-    <cfRule type="dataBar" priority="16">
+    <cfRule type="dataBar" priority="22">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3307,7 +3307,7 @@
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="18">
+    <cfRule type="dataBar" priority="23">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3321,7 +3321,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I50">
-    <cfRule type="colorScale" priority="15">
+    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
